--- a/AutoEIT_Graded_Results.xlsx
+++ b/AutoEIT_Graded_Results.xlsx
@@ -954,7 +954,7 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -968,7 +968,7 @@
         <v>44</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1010,7 +1010,7 @@
         <v>47</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1038,7 +1038,7 @@
         <v>49</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1066,7 +1066,7 @@
         <v>51</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1122,7 +1122,7 @@
         <v>55</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1136,7 +1136,7 @@
         <v>56</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1164,7 +1164,7 @@
         <v>58</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1178,7 +1178,7 @@
         <v>59</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1234,7 +1234,7 @@
         <v>63</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1370,7 +1370,7 @@
         <v>70</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1440,7 +1440,7 @@
         <v>75</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1454,7 +1454,7 @@
         <v>76</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1468,7 +1468,7 @@
         <v>77</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1524,7 +1524,7 @@
         <v>81</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1608,7 +1608,7 @@
         <v>87</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1678,7 +1678,7 @@
         <v>92</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1706,7 +1706,7 @@
         <v>94</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1814,7 +1814,7 @@
         <v>98</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1842,7 +1842,7 @@
         <v>99</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1884,7 +1884,7 @@
         <v>102</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1912,7 +1912,7 @@
         <v>104</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1926,7 +1926,7 @@
         <v>105</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1940,7 +1940,7 @@
         <v>106</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1954,7 +1954,7 @@
         <v>107</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1982,7 +1982,7 @@
         <v>109</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2052,7 +2052,7 @@
         <v>58</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2066,7 +2066,7 @@
         <v>114</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2108,7 +2108,7 @@
         <v>117</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2122,7 +2122,7 @@
         <v>118</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2136,7 +2136,7 @@
         <v>119</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2150,7 +2150,7 @@
         <v>120</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2192,7 +2192,7 @@
         <v>123</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2258,7 +2258,7 @@
         <v>126</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2272,7 +2272,7 @@
         <v>127</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2300,7 +2300,7 @@
         <v>129</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2314,7 +2314,7 @@
         <v>130</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2356,7 +2356,7 @@
         <v>133</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2370,7 +2370,7 @@
         <v>134</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2384,7 +2384,7 @@
         <v>135</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2412,7 +2412,7 @@
         <v>137</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2468,7 +2468,7 @@
         <v>141</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2496,7 +2496,7 @@
         <v>143</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2552,7 +2552,7 @@
         <v>147</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2622,7 +2622,7 @@
         <v>152</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
